--- a/backend/data/financials_by_company/002510.SZ.xlsx
+++ b/backend/data/financials_by_company/002510.SZ.xlsx
@@ -692,231 +692,231 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-24558283.357999</v>
+        <v>-77545774.07250001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.189115</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>410288232.22</v>
+        <v>222180918.24</v>
       </c>
       <c r="E2" t="n">
-        <v>-129858973.32</v>
+        <v>-310183096.29</v>
       </c>
       <c r="F2" t="n">
-        <v>-129858973.32</v>
+        <v>-310183096.29</v>
       </c>
       <c r="G2" t="n">
-        <v>95252769.73999999</v>
+        <v>-211888430.9</v>
       </c>
       <c r="H2" t="n">
-        <v>122871073.49</v>
+        <v>106740301.52</v>
       </c>
       <c r="I2" t="n">
-        <v>2330042494.42</v>
+        <v>1591763922.59</v>
       </c>
       <c r="J2" t="n">
-        <v>280429258.9</v>
+        <v>-88002178.05</v>
       </c>
       <c r="K2" t="n">
-        <v>157558185.41</v>
+        <v>-194742479.57</v>
       </c>
       <c r="L2" t="n">
-        <v>-48789776.76</v>
+        <v>7478688.52</v>
       </c>
       <c r="M2" t="n">
-        <v>54722470.98</v>
+        <v>240911.25</v>
       </c>
       <c r="N2" t="n">
-        <v>7501383.82</v>
+        <v>9648971.109999999</v>
       </c>
       <c r="O2" t="n">
-        <v>200553459.702001</v>
+        <v>20748891.3175</v>
       </c>
       <c r="P2" t="n">
-        <v>95252769.73999999</v>
+        <v>-211888430.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>2579864734.75</v>
+        <v>1787142260.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1663913.99</v>
+        <v>1296640.2</v>
       </c>
       <c r="S2" t="n">
-        <v>103978718.25</v>
+        <v>-196946839.26</v>
       </c>
       <c r="T2" t="n">
-        <v>952527697</v>
+        <v>963129231</v>
       </c>
       <c r="U2" t="n">
-        <v>952527697</v>
+        <v>963129231</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="X2" t="n">
-        <v>95252769.73999999</v>
+        <v>-211888430.9</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>95252769.73999999</v>
+        <v>-211888430.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>11864834.31</v>
+        <v>1685684.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>83387935.43000001</v>
+        <v>-213574115.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>83387935.43000001</v>
+        <v>-213574115.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>19447779</v>
+        <v>18590724.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>102835714.43</v>
+        <v>-194983390.82</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1143003.82</v>
+        <v>-41873328.35</v>
       </c>
       <c r="AG2" t="n">
-        <v>-128125977.15</v>
+        <v>-330078345.02</v>
       </c>
       <c r="AH2" t="n">
-        <v>25587.93</v>
+        <v>-3639749.78</v>
       </c>
       <c r="AI2" t="n">
-        <v>25506782.94</v>
+        <v>95331987.01000001</v>
       </c>
       <c r="AJ2" t="n">
-        <v>102593606.28</v>
+        <v>238386107.79</v>
       </c>
       <c r="AK2" t="n">
-        <v>-48789776.76</v>
+        <v>7478688.52</v>
       </c>
       <c r="AL2" t="n">
-        <v>1568689.6</v>
+        <v>1929371.34</v>
       </c>
       <c r="AM2" t="n">
-        <v>54722470.98</v>
+        <v>240911.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>7501383.82</v>
+        <v>9648971.109999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>165846827.14</v>
+        <v>91900606.45999999</v>
       </c>
       <c r="AP2" t="n">
-        <v>249822240.33</v>
+        <v>195378337.65</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24451587.48</v>
+        <v>15235064.93</v>
       </c>
       <c r="AR2" t="n">
-        <v>6932483.47</v>
+        <v>6852167.61</v>
       </c>
       <c r="AS2" t="n">
-        <v>6932483.47</v>
+        <v>6852167.61</v>
       </c>
       <c r="AT2" t="n">
-        <v>91604928.42</v>
+        <v>68505671.22</v>
       </c>
       <c r="AU2" t="n">
-        <v>60329978.16</v>
+        <v>57970051.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>21229736.48</v>
+        <v>22045859.91</v>
       </c>
       <c r="AW2" t="n">
-        <v>39100241.68</v>
+        <v>35924191.41</v>
       </c>
       <c r="AX2" t="n">
-        <v>1663913.99</v>
+        <v>1296640.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>415669067.47</v>
+        <v>287278944.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2330042494.42</v>
+        <v>1591763922.59</v>
       </c>
       <c r="BA2" t="n">
-        <v>2745711561.89</v>
+        <v>1879042866.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>2745711561.89</v>
+        <v>1879042866.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-17734462.195253</v>
+        <v>-14446547.501886</v>
       </c>
       <c r="C3" t="n">
-        <v>0.184825</v>
+        <v>0.177615</v>
       </c>
       <c r="D3" t="n">
-        <v>333524956.18</v>
+        <v>299756548.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-95952669.45</v>
+        <v>-81336243.95999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-95952669.45</v>
+        <v>-81336243.95999999</v>
       </c>
       <c r="G3" t="n">
-        <v>83619353.03</v>
+        <v>80184453.73</v>
       </c>
       <c r="H3" t="n">
-        <v>83986948.73999999</v>
+        <v>91347521.04000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2380979729.93</v>
+        <v>2159543773.26</v>
       </c>
       <c r="J3" t="n">
-        <v>237572286.73</v>
+        <v>218420304.77</v>
       </c>
       <c r="K3" t="n">
-        <v>153585337.99</v>
+        <v>127072783.73</v>
       </c>
       <c r="L3" t="n">
-        <v>-50137516.58</v>
+        <v>-31036001.83</v>
       </c>
       <c r="M3" t="n">
-        <v>58840041.02</v>
+        <v>35687783.15</v>
       </c>
       <c r="N3" t="n">
-        <v>10182030.38</v>
+        <v>7454662.7</v>
       </c>
       <c r="O3" t="n">
-        <v>161837560.284747</v>
+        <v>147074150.188114</v>
       </c>
       <c r="P3" t="n">
-        <v>83619353.03</v>
+        <v>80184453.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>2641908876.13</v>
+        <v>2410707969.24</v>
       </c>
       <c r="R3" t="n">
-        <v>844410.91</v>
+        <v>1531119.39</v>
       </c>
       <c r="S3" t="n">
-        <v>92761375.65000001</v>
+        <v>89264582.81</v>
       </c>
       <c r="T3" t="n">
-        <v>929103923</v>
+        <v>890938375</v>
       </c>
       <c r="U3" t="n">
-        <v>929103923</v>
+        <v>890938375</v>
       </c>
       <c r="V3" t="n">
         <v>0.09</v>
@@ -925,162 +925,162 @@
         <v>0.09</v>
       </c>
       <c r="X3" t="n">
-        <v>83619353.03</v>
+        <v>80184453.73</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>83619353.03</v>
+        <v>80184453.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>6385365.51</v>
+        <v>5030811.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>77233987.52</v>
+        <v>75153641.87</v>
       </c>
       <c r="AC3" t="n">
-        <v>77233987.52</v>
+        <v>75153641.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>17511309.45</v>
+        <v>16231358.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>94745296.97</v>
+        <v>91385000.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>1146363.91</v>
+        <v>1958613.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>-121092897.57</v>
+        <v>-87589088.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>-5197496.94</v>
+        <v>-119395.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>51719955.91</v>
+        <v>16900297.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>74570438.59999999</v>
+        <v>70808186.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>-50137516.58</v>
+        <v>-31036001.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1479505.94</v>
+        <v>2802881.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>58840041.02</v>
+        <v>35687783.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>10182030.38</v>
+        <v>7454662.7</v>
       </c>
       <c r="AO3" t="n">
-        <v>154265387.12</v>
+        <v>141460389.47</v>
       </c>
       <c r="AP3" t="n">
-        <v>260929146.2</v>
+        <v>251164195.98</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8090749.39</v>
+        <v>20874171.11</v>
       </c>
       <c r="AR3" t="n">
-        <v>6793723.81</v>
+        <v>10880206.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>6793723.81</v>
+        <v>10880206.08</v>
       </c>
       <c r="AT3" t="n">
-        <v>103112836.44</v>
+        <v>97973686.02</v>
       </c>
       <c r="AU3" t="n">
-        <v>79750170.40000001</v>
+        <v>69594820.59</v>
       </c>
       <c r="AV3" t="n">
-        <v>37437138.99</v>
+        <v>33644892.34</v>
       </c>
       <c r="AW3" t="n">
-        <v>42313031.41</v>
+        <v>35949928.25</v>
       </c>
       <c r="AX3" t="n">
-        <v>844410.91</v>
+        <v>1531119.39</v>
       </c>
       <c r="AY3" t="n">
-        <v>415194533.32</v>
+        <v>392624585.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2380979729.93</v>
+        <v>2159543773.26</v>
       </c>
       <c r="BA3" t="n">
-        <v>2796174263.25</v>
+        <v>2552168358.71</v>
       </c>
       <c r="BB3" t="n">
-        <v>2796174263.25</v>
+        <v>2552168358.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-14446547.501886</v>
+        <v>-17734462.195253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.177615</v>
+        <v>0.184825</v>
       </c>
       <c r="D4" t="n">
-        <v>299756548.73</v>
+        <v>333524956.18</v>
       </c>
       <c r="E4" t="n">
-        <v>-81336243.95999999</v>
+        <v>-95952669.45</v>
       </c>
       <c r="F4" t="n">
-        <v>-81336243.95999999</v>
+        <v>-95952669.45</v>
       </c>
       <c r="G4" t="n">
-        <v>80184453.73</v>
+        <v>83619353.03</v>
       </c>
       <c r="H4" t="n">
-        <v>91347521.04000001</v>
+        <v>83986948.73999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2159543773.26</v>
+        <v>2380979729.93</v>
       </c>
       <c r="J4" t="n">
-        <v>218420304.77</v>
+        <v>237572286.73</v>
       </c>
       <c r="K4" t="n">
-        <v>127072783.73</v>
+        <v>153585337.99</v>
       </c>
       <c r="L4" t="n">
-        <v>-31036001.83</v>
+        <v>-50137516.58</v>
       </c>
       <c r="M4" t="n">
-        <v>35687783.15</v>
+        <v>58840041.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7454662.7</v>
+        <v>10182030.38</v>
       </c>
       <c r="O4" t="n">
-        <v>147074150.188114</v>
+        <v>161837560.284747</v>
       </c>
       <c r="P4" t="n">
-        <v>80184453.73</v>
+        <v>83619353.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>2410707969.24</v>
+        <v>2641908876.13</v>
       </c>
       <c r="R4" t="n">
-        <v>1531119.39</v>
+        <v>844410.91</v>
       </c>
       <c r="S4" t="n">
-        <v>89264582.81</v>
+        <v>92761375.65000001</v>
       </c>
       <c r="T4" t="n">
-        <v>890938375</v>
+        <v>929103923</v>
       </c>
       <c r="U4" t="n">
-        <v>890938375</v>
+        <v>929103923</v>
       </c>
       <c r="V4" t="n">
         <v>0.09</v>
@@ -1089,261 +1089,261 @@
         <v>0.09</v>
       </c>
       <c r="X4" t="n">
-        <v>80184453.73</v>
+        <v>83619353.03</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>80184453.73</v>
+        <v>83619353.03</v>
       </c>
       <c r="AA4" t="n">
-        <v>5030811.86</v>
+        <v>6385365.51</v>
       </c>
       <c r="AB4" t="n">
-        <v>75153641.87</v>
+        <v>77233987.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>75153641.87</v>
+        <v>77233987.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>16231358.71</v>
+        <v>17511309.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>91385000.58</v>
+        <v>94745296.97</v>
       </c>
       <c r="AF4" t="n">
-        <v>1958613.32</v>
+        <v>1146363.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>-87589088.31</v>
+        <v>-121092897.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>-119395.19</v>
+        <v>-5197496.94</v>
       </c>
       <c r="AI4" t="n">
-        <v>16900297.3</v>
+        <v>51719955.91</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70808186.2</v>
+        <v>74570438.59999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>-31036001.83</v>
+        <v>-50137516.58</v>
       </c>
       <c r="AL4" t="n">
-        <v>2802881.38</v>
+        <v>1479505.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>35687783.15</v>
+        <v>58840041.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>7454662.7</v>
+        <v>10182030.38</v>
       </c>
       <c r="AO4" t="n">
-        <v>141460389.47</v>
+        <v>154265387.12</v>
       </c>
       <c r="AP4" t="n">
-        <v>251164195.98</v>
+        <v>260929146.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20874171.11</v>
+        <v>8090749.39</v>
       </c>
       <c r="AR4" t="n">
-        <v>10880206.08</v>
+        <v>6793723.81</v>
       </c>
       <c r="AS4" t="n">
-        <v>10880206.08</v>
+        <v>6793723.81</v>
       </c>
       <c r="AT4" t="n">
-        <v>97973686.02</v>
+        <v>103112836.44</v>
       </c>
       <c r="AU4" t="n">
-        <v>69594820.59</v>
+        <v>79750170.40000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>33644892.34</v>
+        <v>37437138.99</v>
       </c>
       <c r="AW4" t="n">
-        <v>35949928.25</v>
+        <v>42313031.41</v>
       </c>
       <c r="AX4" t="n">
-        <v>1531119.39</v>
+        <v>844410.91</v>
       </c>
       <c r="AY4" t="n">
-        <v>392624585.45</v>
+        <v>415194533.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2159543773.26</v>
+        <v>2380979729.93</v>
       </c>
       <c r="BA4" t="n">
-        <v>2552168358.71</v>
+        <v>2796174263.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>2552168358.71</v>
+        <v>2796174263.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-77545774.07250001</v>
+        <v>-24558283.357999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.189115</v>
       </c>
       <c r="D5" t="n">
-        <v>222180918.24</v>
+        <v>410288232.22</v>
       </c>
       <c r="E5" t="n">
-        <v>-310183096.29</v>
+        <v>-129858973.32</v>
       </c>
       <c r="F5" t="n">
-        <v>-310183096.29</v>
+        <v>-129858973.32</v>
       </c>
       <c r="G5" t="n">
-        <v>-211888430.9</v>
+        <v>95252769.73999999</v>
       </c>
       <c r="H5" t="n">
-        <v>106740301.52</v>
+        <v>122871073.49</v>
       </c>
       <c r="I5" t="n">
-        <v>1591763922.59</v>
+        <v>2330042494.42</v>
       </c>
       <c r="J5" t="n">
-        <v>-88002178.05</v>
+        <v>280429258.9</v>
       </c>
       <c r="K5" t="n">
-        <v>-194742479.57</v>
+        <v>157558185.41</v>
       </c>
       <c r="L5" t="n">
-        <v>7478688.52</v>
+        <v>-48789776.76</v>
       </c>
       <c r="M5" t="n">
-        <v>240911.25</v>
+        <v>54722470.98</v>
       </c>
       <c r="N5" t="n">
-        <v>9648971.109999999</v>
+        <v>7501383.82</v>
       </c>
       <c r="O5" t="n">
-        <v>20748891.3175</v>
+        <v>200553459.702001</v>
       </c>
       <c r="P5" t="n">
-        <v>-211888430.9</v>
+        <v>95252769.73999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>1787142260.24</v>
+        <v>2579864734.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1296640.2</v>
+        <v>1663913.99</v>
       </c>
       <c r="S5" t="n">
-        <v>-196946839.26</v>
+        <v>103978718.25</v>
       </c>
       <c r="T5" t="n">
-        <v>963129231</v>
+        <v>952527697</v>
       </c>
       <c r="U5" t="n">
-        <v>963129231</v>
+        <v>952527697</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.22</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.22</v>
+        <v>0.1</v>
       </c>
       <c r="X5" t="n">
-        <v>-211888430.9</v>
+        <v>95252769.73999999</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-211888430.9</v>
+        <v>95252769.73999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>1685684.72</v>
+        <v>11864834.31</v>
       </c>
       <c r="AB5" t="n">
-        <v>-213574115.62</v>
+        <v>83387935.43000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-213574115.62</v>
+        <v>83387935.43000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>18590724.8</v>
+        <v>19447779</v>
       </c>
       <c r="AE5" t="n">
-        <v>-194983390.82</v>
+        <v>102835714.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>-41873328.35</v>
+        <v>-1143003.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>-330078345.02</v>
+        <v>-128125977.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3639749.78</v>
+        <v>25587.93</v>
       </c>
       <c r="AI5" t="n">
-        <v>95331987.01000001</v>
+        <v>25506782.94</v>
       </c>
       <c r="AJ5" t="n">
-        <v>238386107.79</v>
+        <v>102593606.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>7478688.52</v>
+        <v>-48789776.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>1929371.34</v>
+        <v>1568689.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>240911.25</v>
+        <v>54722470.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>9648971.109999999</v>
+        <v>7501383.82</v>
       </c>
       <c r="AO5" t="n">
-        <v>91900606.45999999</v>
+        <v>165846827.14</v>
       </c>
       <c r="AP5" t="n">
-        <v>195378337.65</v>
+        <v>249822240.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15235064.93</v>
+        <v>24451587.48</v>
       </c>
       <c r="AR5" t="n">
-        <v>6852167.61</v>
+        <v>6932483.47</v>
       </c>
       <c r="AS5" t="n">
-        <v>6852167.61</v>
+        <v>6932483.47</v>
       </c>
       <c r="AT5" t="n">
-        <v>68505671.22</v>
+        <v>91604928.42</v>
       </c>
       <c r="AU5" t="n">
-        <v>57970051.32</v>
+        <v>60329978.16</v>
       </c>
       <c r="AV5" t="n">
-        <v>22045859.91</v>
+        <v>21229736.48</v>
       </c>
       <c r="AW5" t="n">
-        <v>35924191.41</v>
+        <v>39100241.68</v>
       </c>
       <c r="AX5" t="n">
-        <v>1296640.2</v>
+        <v>1663913.99</v>
       </c>
       <c r="AY5" t="n">
-        <v>287278944.11</v>
+        <v>415669067.47</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1591763922.59</v>
+        <v>2330042494.42</v>
       </c>
       <c r="BA5" t="n">
-        <v>1879042866.7</v>
+        <v>2745711561.89</v>
       </c>
       <c r="BB5" t="n">
-        <v>1879042866.7</v>
+        <v>2745711561.89</v>
       </c>
     </row>
   </sheetData>
@@ -1724,300 +1724,434 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>941616619</v>
+      </c>
+      <c r="C2" t="n">
+        <v>941616619</v>
+      </c>
+      <c r="D2" t="n">
+        <v>279007232.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1008272519.62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1821723399.82</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2919178014.62</v>
+      </c>
+      <c r="H2" t="n">
+        <v>448031544.49</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1821723399.82</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1544995.05</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1915813754.31</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2190412035.04</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1933080807.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17267052.81</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1915813754.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>58259794.36</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-32003249.66</v>
+      </c>
+      <c r="R2" t="n">
+        <v>723100058.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>941616619</v>
+      </c>
+      <c r="T2" t="n">
+        <v>941616619</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3028737781.62</v>
+      </c>
+      <c r="V2" t="n">
+        <v>344710632.86</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1937644.66</v>
+      </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>64042621.68</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2587090.74</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>276143275.78</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1544995.05</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>274598280.73</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2684027148.76</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>41464363.7</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>732129243.84</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>728765979.58</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>911784031.4</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>22767451.41</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>82131041.87</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>806585538.12</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>4961818588.74</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1829759895.49</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3245484.84</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>178139588.23</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>92055732.06</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>92055732.06</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>645427948.96</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>66019634.06</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>94090354.48999999</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>94090354.48999999</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>737858717.61</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-1067459894.38</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1805318611.99</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>11412677.97</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>71054406.56</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1229942221.26</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>492909306.2</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3132058693.25</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3385602.62</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>89273145.66</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1527651212.92</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>-288463607.19</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1079835799.55</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>864602342.74</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>614059467.66</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>48989402.52</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>207691056.56</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>579700647.58</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="n">
+        <v>724357027.91</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>724357027.91</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>260973944.72</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>463383083.19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1015138708</v>
+        <v>941645290</v>
       </c>
       <c r="C3" t="n">
-        <v>1015138708</v>
+        <v>941645290</v>
       </c>
       <c r="D3" t="n">
-        <v>426584068.73</v>
+        <v>345563203.13</v>
       </c>
       <c r="E3" t="n">
-        <v>1251149832.24</v>
+        <v>1279848214.91</v>
       </c>
       <c r="F3" t="n">
-        <v>2361140702.07</v>
+        <v>1898850933.17</v>
       </c>
       <c r="G3" t="n">
-        <v>3602098407.02</v>
+        <v>3284903330.41</v>
       </c>
       <c r="H3" t="n">
-        <v>870658210.4299999</v>
+        <v>691337758.41</v>
       </c>
       <c r="I3" t="n">
-        <v>2361140702.07</v>
+        <v>1898850933.17</v>
       </c>
       <c r="J3" t="n">
-        <v>15999586.05</v>
+        <v>511865.84</v>
       </c>
       <c r="K3" t="n">
-        <v>2477729846.58</v>
+        <v>2021025443.79</v>
       </c>
       <c r="L3" t="n">
-        <v>3148497500.83</v>
+        <v>2630113710.12</v>
       </c>
       <c r="M3" t="n">
-        <v>2472615887.71</v>
+        <v>2033261684.74</v>
       </c>
       <c r="N3" t="n">
-        <v>-5113958.87</v>
+        <v>12236240.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2477729846.58</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>2021025443.79</v>
+      </c>
+      <c r="P3" t="n">
+        <v>58236997.15</v>
+      </c>
       <c r="Q3" t="n">
-        <v>197234428.11</v>
+        <v>48181204.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1009660842.87</v>
+        <v>723192665.4299999</v>
       </c>
       <c r="S3" t="n">
-        <v>1015138708</v>
+        <v>941645290</v>
       </c>
       <c r="T3" t="n">
-        <v>1015138708</v>
+        <v>941645290</v>
       </c>
       <c r="U3" t="n">
-        <v>3530647242.85</v>
+        <v>3714821633.4</v>
       </c>
       <c r="V3" t="n">
-        <v>794830158.23</v>
+        <v>682327956.48</v>
       </c>
       <c r="W3" t="n">
-        <v>22119601.29</v>
-      </c>
-      <c r="X3" t="n">
-        <v>14200000</v>
-      </c>
+        <v>4624626.18</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>54350870.94</v>
+        <v>60025328.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>17392445.7</v>
+        <v>8077869.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>686767240.3</v>
+        <v>609600132.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>15999586.05</v>
+        <v>511865.84</v>
       </c>
       <c r="AC3" t="n">
-        <v>670767654.25</v>
+        <v>609088266.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>2735817084.62</v>
+        <v>3032493676.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>99979958.95999999</v>
+        <v>80798876.43000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>564382591.9400001</v>
+        <v>670248082.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>453600906.19</v>
+        <v>654789620.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1171204268.34</v>
+        <v>1243913361.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>57283738.44</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>18750075.98</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>300000</v>
+      </c>
       <c r="AK3" t="n">
-        <v>98020794.34999999</v>
+        <v>62640926.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>1015899735.55</v>
+        <v>1162222358.76</v>
       </c>
       <c r="AM3" t="n">
-        <v>6003263130.56</v>
+        <v>5748083318.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>2396787835.51</v>
+        <v>2024251882.81</v>
       </c>
       <c r="AO3" t="n">
-        <v>1756834.37</v>
+        <v>28354402.77</v>
       </c>
       <c r="AP3" t="n">
-        <v>8947387.949999999</v>
+        <v>4183201.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>187089905.52</v>
+        <v>179933340.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>76715808.37</v>
+        <v>93642866.02</v>
       </c>
       <c r="AS3" t="n">
-        <v>76715808.37</v>
+        <v>93642866.02</v>
       </c>
       <c r="AT3" t="n">
-        <v>870753135.23</v>
+        <v>719239237.99</v>
       </c>
       <c r="AU3" t="n">
-        <v>68013855.36</v>
+        <v>72409264.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>116589144.51</v>
+        <v>122174510.62</v>
       </c>
       <c r="AW3" t="n">
-        <v>116589144.51</v>
+        <v>122174510.62</v>
       </c>
       <c r="AX3" t="n">
-        <v>1065583111.42</v>
+        <v>801754239.84</v>
       </c>
       <c r="AY3" t="n">
-        <v>-1247537200.96</v>
+        <v>-1138464994.78</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2313120312.38</v>
+        <v>1940219234.62</v>
       </c>
       <c r="BA3" t="n">
-        <v>16699838.66</v>
+        <v>120394895.98</v>
       </c>
       <c r="BB3" t="n">
-        <v>93257032.48999999</v>
+        <v>65441248.72</v>
       </c>
       <c r="BC3" t="n">
-        <v>1561734491.24</v>
+        <v>1250825820.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>641428949.99</v>
+        <v>503557269.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>3606475295.05</v>
+        <v>3723831435.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>11138417.81</v>
+        <v>10745170.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>6942948.32</v>
+        <v>64539999.24</v>
       </c>
       <c r="BH3" t="n">
-        <v>1519226788.03</v>
+        <v>1802477590.12</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2295613.4</v>
+        <v>15723599.22</v>
       </c>
       <c r="BK3" t="n">
-        <v>931101754.51</v>
+        <v>1013924659.91</v>
       </c>
       <c r="BL3" t="n">
-        <v>496468134.93</v>
+        <v>693691954.9299999</v>
       </c>
       <c r="BM3" t="n">
-        <v>89361285.19</v>
+        <v>79137376.06</v>
       </c>
       <c r="BN3" t="n">
-        <v>392235301.02</v>
+        <v>296469464.95</v>
       </c>
       <c r="BO3" t="n">
-        <v>979147348.16</v>
+        <v>631284526.63</v>
       </c>
       <c r="BP3" t="n">
-        <v>-267267997.49</v>
+        <v>-368891185.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1246415345.65</v>
+        <v>1000175712.43</v>
       </c>
       <c r="BR3" t="n">
-        <v>697784491.71</v>
+        <v>918314683.49</v>
       </c>
       <c r="BS3" t="n">
-        <v>697784491.71</v>
+        <v>918314683.49</v>
       </c>
       <c r="BT3" t="n">
-        <v>112835137.12</v>
+        <v>375922280.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>584949354.59</v>
+        <v>542392402.8200001</v>
       </c>
     </row>
     <row r="4">
@@ -2241,435 +2375,301 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>941645290</v>
+        <v>1015138708</v>
       </c>
       <c r="C5" t="n">
-        <v>941645290</v>
+        <v>1015138708</v>
       </c>
       <c r="D5" t="n">
-        <v>345563203.13</v>
+        <v>426584068.73</v>
       </c>
       <c r="E5" t="n">
-        <v>1279848214.91</v>
+        <v>1251149832.24</v>
       </c>
       <c r="F5" t="n">
-        <v>1898850933.17</v>
+        <v>2361140702.07</v>
       </c>
       <c r="G5" t="n">
-        <v>3284903330.41</v>
+        <v>3602098407.02</v>
       </c>
       <c r="H5" t="n">
-        <v>691337758.41</v>
+        <v>870658210.4299999</v>
       </c>
       <c r="I5" t="n">
-        <v>1898850933.17</v>
+        <v>2361140702.07</v>
       </c>
       <c r="J5" t="n">
-        <v>511865.84</v>
+        <v>15999586.05</v>
       </c>
       <c r="K5" t="n">
-        <v>2021025443.79</v>
+        <v>2477729846.58</v>
       </c>
       <c r="L5" t="n">
-        <v>2630113710.12</v>
+        <v>3148497500.83</v>
       </c>
       <c r="M5" t="n">
-        <v>2033261684.74</v>
+        <v>2472615887.71</v>
       </c>
       <c r="N5" t="n">
-        <v>12236240.95</v>
+        <v>-5113958.87</v>
       </c>
       <c r="O5" t="n">
-        <v>2021025443.79</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58236997.15</v>
-      </c>
+        <v>2477729846.58</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>48181204.07</v>
+        <v>197234428.11</v>
       </c>
       <c r="R5" t="n">
-        <v>723192665.4299999</v>
+        <v>1009660842.87</v>
       </c>
       <c r="S5" t="n">
-        <v>941645290</v>
+        <v>1015138708</v>
       </c>
       <c r="T5" t="n">
-        <v>941645290</v>
+        <v>1015138708</v>
       </c>
       <c r="U5" t="n">
-        <v>3714821633.4</v>
+        <v>3530647242.85</v>
       </c>
       <c r="V5" t="n">
-        <v>682327956.48</v>
+        <v>794830158.23</v>
       </c>
       <c r="W5" t="n">
-        <v>4624626.18</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>22119601.29</v>
+      </c>
+      <c r="X5" t="n">
+        <v>14200000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>60025328.21</v>
+        <v>54350870.94</v>
       </c>
       <c r="Z5" t="n">
-        <v>8077869.92</v>
+        <v>17392445.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>609600132.17</v>
+        <v>686767240.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>511865.84</v>
+        <v>15999586.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>609088266.33</v>
+        <v>670767654.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>3032493676.92</v>
+        <v>2735817084.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>80798876.43000001</v>
+        <v>99979958.95999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>670248082.74</v>
+        <v>564382591.9400001</v>
       </c>
       <c r="AG5" t="n">
-        <v>654789620.29</v>
+        <v>453600906.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1243913361.03</v>
+        <v>1171204268.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>18750075.98</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>300000</v>
-      </c>
+        <v>57283738.44</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>62640926.29</v>
+        <v>98020794.34999999</v>
       </c>
       <c r="AL5" t="n">
-        <v>1162222358.76</v>
+        <v>1015899735.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>5748083318.14</v>
+        <v>6003263130.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>2024251882.81</v>
+        <v>2396787835.51</v>
       </c>
       <c r="AO5" t="n">
-        <v>28354402.77</v>
+        <v>1756834.37</v>
       </c>
       <c r="AP5" t="n">
-        <v>4183201.7</v>
+        <v>8947387.949999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>179933340.6</v>
+        <v>187089905.52</v>
       </c>
       <c r="AR5" t="n">
-        <v>93642866.02</v>
+        <v>76715808.37</v>
       </c>
       <c r="AS5" t="n">
-        <v>93642866.02</v>
+        <v>76715808.37</v>
       </c>
       <c r="AT5" t="n">
-        <v>719239237.99</v>
+        <v>870753135.23</v>
       </c>
       <c r="AU5" t="n">
-        <v>72409264.08</v>
+        <v>68013855.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>122174510.62</v>
+        <v>116589144.51</v>
       </c>
       <c r="AW5" t="n">
-        <v>122174510.62</v>
+        <v>116589144.51</v>
       </c>
       <c r="AX5" t="n">
-        <v>801754239.84</v>
+        <v>1065583111.42</v>
       </c>
       <c r="AY5" t="n">
-        <v>-1138464994.78</v>
+        <v>-1247537200.96</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1940219234.62</v>
+        <v>2313120312.38</v>
       </c>
       <c r="BA5" t="n">
-        <v>120394895.98</v>
+        <v>16699838.66</v>
       </c>
       <c r="BB5" t="n">
-        <v>65441248.72</v>
+        <v>93257032.48999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>1250825820.78</v>
+        <v>1561734491.24</v>
       </c>
       <c r="BD5" t="n">
-        <v>503557269.14</v>
+        <v>641428949.99</v>
       </c>
       <c r="BE5" t="n">
-        <v>3723831435.33</v>
+        <v>3606475295.05</v>
       </c>
       <c r="BF5" t="n">
-        <v>10745170.9</v>
+        <v>11138417.81</v>
       </c>
       <c r="BG5" t="n">
-        <v>64539999.24</v>
+        <v>6942948.32</v>
       </c>
       <c r="BH5" t="n">
-        <v>1802477590.12</v>
+        <v>1519226788.03</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>15723599.22</v>
+        <v>2295613.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>1013924659.91</v>
+        <v>931101754.51</v>
       </c>
       <c r="BL5" t="n">
-        <v>693691954.9299999</v>
+        <v>496468134.93</v>
       </c>
       <c r="BM5" t="n">
-        <v>79137376.06</v>
+        <v>89361285.19</v>
       </c>
       <c r="BN5" t="n">
-        <v>296469464.95</v>
+        <v>392235301.02</v>
       </c>
       <c r="BO5" t="n">
-        <v>631284526.63</v>
+        <v>979147348.16</v>
       </c>
       <c r="BP5" t="n">
-        <v>-368891185.8</v>
+        <v>-267267997.49</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1000175712.43</v>
+        <v>1246415345.65</v>
       </c>
       <c r="BR5" t="n">
-        <v>918314683.49</v>
+        <v>697784491.71</v>
       </c>
       <c r="BS5" t="n">
-        <v>918314683.49</v>
+        <v>697784491.71</v>
       </c>
       <c r="BT5" t="n">
-        <v>375922280.67</v>
+        <v>112835137.12</v>
       </c>
       <c r="BU5" t="n">
-        <v>542392402.8200001</v>
+        <v>584949354.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>941616619</v>
-      </c>
-      <c r="C6" t="n">
-        <v>941616619</v>
-      </c>
-      <c r="D6" t="n">
-        <v>279007232.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1008272519.62</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1821723399.82</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2919178014.62</v>
-      </c>
-      <c r="H6" t="n">
-        <v>448031544.49</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1821723399.82</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1544995.05</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1915813754.31</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2190412035.04</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1933080807.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>17267052.81</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1915813754.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>58259794.36</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-32003249.66</v>
-      </c>
-      <c r="R6" t="n">
-        <v>723100058.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>941616619</v>
-      </c>
-      <c r="T6" t="n">
-        <v>941616619</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3028737781.62</v>
-      </c>
-      <c r="V6" t="n">
-        <v>344710632.86</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1937644.66</v>
-      </c>
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>64042621.68</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2587090.74</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>276143275.78</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1544995.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>274598280.73</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2684027148.76</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>41464363.7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>732129243.84</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>728765979.58</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>911784031.4</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>22767451.41</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>82131041.87</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>806585538.12</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>4961818588.74</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1829759895.49</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3245484.84</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>178139588.23</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>92055732.06</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>92055732.06</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>645427948.96</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>66019634.06</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>94090354.48999999</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>94090354.48999999</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>737858717.61</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1067459894.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1805318611.99</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>11412677.97</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>71054406.56</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1229942221.26</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>492909306.2</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3132058693.25</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3385602.62</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>89273145.66</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1527651212.92</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>864602342.74</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>614059467.66</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>48989402.52</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>207691056.56</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>579700647.58</v>
-      </c>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="n">
-        <v>724357027.91</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>724357027.91</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>260973944.72</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>463383083.19</v>
-      </c>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>-288463607.19</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1079835799.55</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2919,558 +2919,558 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>39614120.76</v>
+        <v>133421224.57</v>
       </c>
       <c r="C2" t="n">
-        <v>-806022329.89</v>
+        <v>-629346250</v>
       </c>
       <c r="D2" t="n">
-        <v>807938672.47</v>
+        <v>279805113</v>
       </c>
       <c r="E2" t="n">
-        <v>-111333019.84</v>
+        <v>-30723332.48</v>
       </c>
       <c r="F2" t="n">
-        <v>584949354.59</v>
+        <v>463383083.19</v>
       </c>
       <c r="G2" t="n">
-        <v>608983988.9299999</v>
+        <v>654056156.33</v>
       </c>
       <c r="H2" t="n">
-        <v>3619893.99</v>
+        <v>-2238325.87</v>
       </c>
       <c r="I2" t="n">
-        <v>-27654528.33</v>
+        <v>-188434747.27</v>
       </c>
       <c r="J2" t="n">
-        <v>-84811069.98</v>
+        <v>-734221823.74</v>
       </c>
       <c r="K2" t="n">
-        <v>-12299859.78</v>
+        <v>-357779314.98</v>
       </c>
       <c r="L2" t="n">
-        <v>-74427552.78</v>
+        <v>-26901371.76</v>
       </c>
       <c r="M2" t="n">
-        <v>1916342.58</v>
+        <v>-349541137</v>
       </c>
       <c r="N2" t="n">
-        <v>1916342.58</v>
+        <v>-349541137</v>
       </c>
       <c r="O2" t="n">
-        <v>-806022329.89</v>
+        <v>-629346250</v>
       </c>
       <c r="P2" t="n">
-        <v>807938672.47</v>
+        <v>279805113</v>
       </c>
       <c r="Q2" t="n">
-        <v>-93790598.95</v>
+        <v>381642519.42</v>
       </c>
       <c r="R2" t="n">
-        <v>22593112.38</v>
+        <v>369991509.32</v>
       </c>
       <c r="S2" t="n">
-        <v>22593112.38</v>
+        <v>369991509.32</v>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-5705509.54</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-5705509.54</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-110678201.79</v>
+        <v>11651010.1</v>
       </c>
       <c r="X2" t="n">
-        <v>654818.05</v>
+        <v>42374342.58</v>
       </c>
       <c r="Y2" t="n">
-        <v>-111333019.84</v>
+        <v>-30723332.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>150947140.6</v>
+        <v>164144557.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>-127184095.36</v>
+        <v>-27182300.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>2641825.14</v>
+        <v>-1567236.46</v>
       </c>
       <c r="AC2" t="n">
-        <v>-222598289.24</v>
+        <v>253856378.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>133237458.48</v>
+        <v>-406170151.09</v>
       </c>
       <c r="AE2" t="n">
-        <v>-40465089.74</v>
+        <v>126698709.34</v>
       </c>
       <c r="AF2" t="n">
-        <v>57678486.78</v>
+        <v>49251189.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>122871073.49</v>
+        <v>106740301.52</v>
       </c>
       <c r="AH2" t="n">
-        <v>3224708.58</v>
+        <v>2947105.45</v>
       </c>
       <c r="AI2" t="n">
-        <v>119646364.91</v>
+        <v>103793196.07</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-115081626.57</v>
+        <v>-81444246.01000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>1174977.61</v>
+        <v>-3364367.01</v>
       </c>
       <c r="AL2" t="n">
-        <v>83387935.43000001</v>
+        <v>-213574115.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>150947140.6</v>
+        <v>164144557.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>-84853049.91</v>
+        <v>-65264094.17</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1963445822.06</v>
+        <v>-1749168424.96</v>
       </c>
       <c r="AP2" t="n">
-        <v>-280594148.76</v>
+        <v>-312017364.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-421895746.12</v>
+        <v>-312976039.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1260955927.18</v>
+        <v>-1124175020.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>2199246012.57</v>
+        <v>1978577076.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>94176294.34</v>
+        <v>101141233.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>2105069718.23</v>
+        <v>1877435842.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-254912222.83</v>
+        <v>-171958749.35</v>
       </c>
       <c r="C3" t="n">
-        <v>-463009098.83</v>
+        <v>-258105113</v>
       </c>
       <c r="D3" t="n">
-        <v>774419833.39</v>
+        <v>687594404.83</v>
       </c>
       <c r="E3" t="n">
-        <v>-309085179.23</v>
+        <v>-162395630.91</v>
       </c>
       <c r="F3" t="n">
-        <v>608983988.9299999</v>
+        <v>542392402.8200001</v>
       </c>
       <c r="G3" t="n">
-        <v>542392402.8200001</v>
+        <v>463383083.19</v>
       </c>
       <c r="H3" t="n">
-        <v>4151432.73</v>
+        <v>4428360.02</v>
       </c>
       <c r="I3" t="n">
-        <v>62440153.38</v>
+        <v>74580959.61</v>
       </c>
       <c r="J3" t="n">
-        <v>264401682.01</v>
+        <v>201504396.38</v>
       </c>
       <c r="K3" t="n">
-        <v>-11285499.29</v>
+        <v>-207203927.65</v>
       </c>
       <c r="L3" t="n">
-        <v>-35723553.26</v>
+        <v>-20780967.8</v>
       </c>
       <c r="M3" t="n">
-        <v>311410734.56</v>
+        <v>429489291.83</v>
       </c>
       <c r="N3" t="n">
-        <v>311410734.56</v>
+        <v>429489291.83</v>
       </c>
       <c r="O3" t="n">
-        <v>-463009098.83</v>
+        <v>-258105113</v>
       </c>
       <c r="P3" t="n">
-        <v>774419833.39</v>
+        <v>687594404.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>-256134485.03</v>
+        <v>-117360318.33</v>
       </c>
       <c r="R3" t="n">
-        <v>52508882.62</v>
+        <v>44724710.39</v>
       </c>
       <c r="S3" t="n">
-        <v>52509050.62</v>
+        <v>50785710.39</v>
       </c>
       <c r="T3" t="n">
-        <v>-168</v>
+        <v>-6061000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-308643367.65</v>
+        <v>-162085028.72</v>
       </c>
       <c r="X3" t="n">
-        <v>441811.58</v>
+        <v>310602.19</v>
       </c>
       <c r="Y3" t="n">
-        <v>-309085179.23</v>
+        <v>-162395630.91</v>
       </c>
       <c r="Z3" t="n">
-        <v>54172956.4</v>
+        <v>-9563118.439999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>-180126807.72</v>
+        <v>-235586420.37</v>
       </c>
       <c r="AB3" t="n">
-        <v>-483814.28</v>
+        <v>3697026.81</v>
       </c>
       <c r="AC3" t="n">
-        <v>-73158674.20999999</v>
+        <v>250970402.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>157196489.34</v>
+        <v>-303936085.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>-263680808.57</v>
+        <v>-186317763.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>69061704.70999999</v>
+        <v>31600443.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>83986948.73999999</v>
+        <v>91347521.04000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>3183237.47</v>
+        <v>2781639.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>80803711.27</v>
+        <v>88565881.89</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-117205855.04</v>
+        <v>-60130040.76</v>
       </c>
       <c r="AK3" t="n">
-        <v>-5067416.32</v>
+        <v>343252.42</v>
       </c>
       <c r="AL3" t="n">
-        <v>77233987.52</v>
+        <v>75153641.87</v>
       </c>
       <c r="AM3" t="n">
-        <v>54172956.4</v>
+        <v>-9563118.439999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>-43899296.86</v>
+        <v>-80449429.70999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2338667368.42</v>
+        <v>-2219914693.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>-428979706.47</v>
+        <v>-588245519.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-388705859.5</v>
+        <v>-354604345.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1520981802.45</v>
+        <v>-1277064828.89</v>
       </c>
       <c r="AS3" t="n">
-        <v>2436739621.68</v>
+        <v>2290801005.07</v>
       </c>
       <c r="AT3" t="n">
-        <v>112031012.44</v>
+        <v>74627403.86</v>
       </c>
       <c r="AU3" t="n">
-        <v>2324708609.24</v>
+        <v>2216173601.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-171958749.35</v>
+        <v>-254912222.83</v>
       </c>
       <c r="C4" t="n">
-        <v>-258105113</v>
+        <v>-463009098.83</v>
       </c>
       <c r="D4" t="n">
-        <v>687594404.83</v>
+        <v>774419833.39</v>
       </c>
       <c r="E4" t="n">
-        <v>-162395630.91</v>
+        <v>-309085179.23</v>
       </c>
       <c r="F4" t="n">
+        <v>608983988.9299999</v>
+      </c>
+      <c r="G4" t="n">
         <v>542392402.8200001</v>
       </c>
-      <c r="G4" t="n">
-        <v>463383083.19</v>
-      </c>
       <c r="H4" t="n">
-        <v>4428360.02</v>
+        <v>4151432.73</v>
       </c>
       <c r="I4" t="n">
-        <v>74580959.61</v>
+        <v>62440153.38</v>
       </c>
       <c r="J4" t="n">
-        <v>201504396.38</v>
+        <v>264401682.01</v>
       </c>
       <c r="K4" t="n">
-        <v>-207203927.65</v>
+        <v>-11285499.29</v>
       </c>
       <c r="L4" t="n">
-        <v>-20780967.8</v>
+        <v>-35723553.26</v>
       </c>
       <c r="M4" t="n">
-        <v>429489291.83</v>
+        <v>311410734.56</v>
       </c>
       <c r="N4" t="n">
-        <v>429489291.83</v>
+        <v>311410734.56</v>
       </c>
       <c r="O4" t="n">
-        <v>-258105113</v>
+        <v>-463009098.83</v>
       </c>
       <c r="P4" t="n">
-        <v>687594404.83</v>
+        <v>774419833.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>-117360318.33</v>
+        <v>-256134485.03</v>
       </c>
       <c r="R4" t="n">
-        <v>44724710.39</v>
+        <v>52508882.62</v>
       </c>
       <c r="S4" t="n">
-        <v>50785710.39</v>
+        <v>52509050.62</v>
       </c>
       <c r="T4" t="n">
-        <v>-6061000</v>
+        <v>-168</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-162085028.72</v>
+        <v>-308643367.65</v>
       </c>
       <c r="X4" t="n">
-        <v>310602.19</v>
+        <v>441811.58</v>
       </c>
       <c r="Y4" t="n">
-        <v>-162395630.91</v>
+        <v>-309085179.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>-9563118.439999999</v>
+        <v>54172956.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>-235586420.37</v>
+        <v>-180126807.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>3697026.81</v>
+        <v>-483814.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>250970402.16</v>
+        <v>-73158674.20999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>-303936085.61</v>
+        <v>157196489.34</v>
       </c>
       <c r="AE4" t="n">
-        <v>-186317763.73</v>
+        <v>-263680808.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>31600443.86</v>
+        <v>69061704.70999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>91347521.04000001</v>
+        <v>83986948.73999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>2781639.15</v>
+        <v>3183237.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>88565881.89</v>
+        <v>80803711.27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-60130040.76</v>
+        <v>-117205855.04</v>
       </c>
       <c r="AK4" t="n">
-        <v>343252.42</v>
+        <v>-5067416.32</v>
       </c>
       <c r="AL4" t="n">
-        <v>75153641.87</v>
+        <v>77233987.52</v>
       </c>
       <c r="AM4" t="n">
-        <v>-9563118.439999999</v>
+        <v>54172956.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>-80449429.70999999</v>
+        <v>-43899296.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>-2219914693.8</v>
+        <v>-2338667368.42</v>
       </c>
       <c r="AP4" t="n">
-        <v>-588245519.14</v>
+        <v>-428979706.47</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-354604345.77</v>
+        <v>-388705859.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1277064828.89</v>
+        <v>-1520981802.45</v>
       </c>
       <c r="AS4" t="n">
-        <v>2290801005.07</v>
+        <v>2436739621.68</v>
       </c>
       <c r="AT4" t="n">
-        <v>74627403.86</v>
+        <v>112031012.44</v>
       </c>
       <c r="AU4" t="n">
-        <v>2216173601.21</v>
+        <v>2324708609.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>133421224.57</v>
+        <v>39614120.76</v>
       </c>
       <c r="C5" t="n">
-        <v>-629346250</v>
+        <v>-806022329.89</v>
       </c>
       <c r="D5" t="n">
-        <v>279805113</v>
+        <v>807938672.47</v>
       </c>
       <c r="E5" t="n">
-        <v>-30723332.48</v>
+        <v>-111333019.84</v>
       </c>
       <c r="F5" t="n">
-        <v>463383083.19</v>
+        <v>584949354.59</v>
       </c>
       <c r="G5" t="n">
-        <v>654056156.33</v>
+        <v>608983988.9299999</v>
       </c>
       <c r="H5" t="n">
-        <v>-2238325.87</v>
+        <v>3619893.99</v>
       </c>
       <c r="I5" t="n">
-        <v>-188434747.27</v>
+        <v>-27654528.33</v>
       </c>
       <c r="J5" t="n">
-        <v>-734221823.74</v>
+        <v>-84811069.98</v>
       </c>
       <c r="K5" t="n">
-        <v>-357779314.98</v>
+        <v>-12299859.78</v>
       </c>
       <c r="L5" t="n">
-        <v>-26901371.76</v>
+        <v>-74427552.78</v>
       </c>
       <c r="M5" t="n">
-        <v>-349541137</v>
+        <v>1916342.58</v>
       </c>
       <c r="N5" t="n">
-        <v>-349541137</v>
+        <v>1916342.58</v>
       </c>
       <c r="O5" t="n">
-        <v>-629346250</v>
+        <v>-806022329.89</v>
       </c>
       <c r="P5" t="n">
-        <v>279805113</v>
+        <v>807938672.47</v>
       </c>
       <c r="Q5" t="n">
-        <v>381642519.42</v>
+        <v>-93790598.95</v>
       </c>
       <c r="R5" t="n">
-        <v>369991509.32</v>
+        <v>22593112.38</v>
       </c>
       <c r="S5" t="n">
-        <v>369991509.32</v>
+        <v>22593112.38</v>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>-5705509.54</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-5705509.54</v>
+      </c>
       <c r="W5" t="n">
-        <v>11651010.1</v>
+        <v>-110678201.79</v>
       </c>
       <c r="X5" t="n">
-        <v>42374342.58</v>
+        <v>654818.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>-30723332.48</v>
+        <v>-111333019.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>164144557.05</v>
+        <v>150947140.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>-27182300.18</v>
+        <v>-127184095.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1567236.46</v>
+        <v>2641825.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>253856378.03</v>
+        <v>-222598289.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>-406170151.09</v>
+        <v>133237458.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>126698709.34</v>
+        <v>-40465089.74</v>
       </c>
       <c r="AF5" t="n">
-        <v>49251189.55</v>
+        <v>57678486.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>106740301.52</v>
+        <v>122871073.49</v>
       </c>
       <c r="AH5" t="n">
-        <v>2947105.45</v>
+        <v>3224708.58</v>
       </c>
       <c r="AI5" t="n">
-        <v>103793196.07</v>
+        <v>119646364.91</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-81444246.01000001</v>
+        <v>-115081626.57</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3364367.01</v>
+        <v>1174977.61</v>
       </c>
       <c r="AL5" t="n">
-        <v>-213574115.62</v>
+        <v>83387935.43000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>164144557.05</v>
+        <v>150947140.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>-65264094.17</v>
+        <v>-84853049.91</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1749168424.96</v>
+        <v>-1963445822.06</v>
       </c>
       <c r="AP5" t="n">
-        <v>-312017364.12</v>
+        <v>-280594148.76</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-312976039.9</v>
+        <v>-421895746.12</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1124175020.94</v>
+        <v>-1260955927.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>1978577076.18</v>
+        <v>2199246012.57</v>
       </c>
       <c r="AT5" t="n">
-        <v>101141233.75</v>
+        <v>94176294.34</v>
       </c>
       <c r="AU5" t="n">
-        <v>1877435842.43</v>
+        <v>2105069718.23</v>
       </c>
     </row>
   </sheetData>
@@ -3484,7 +3484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3655,590 +3655,595 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4340,34 +4345,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6.73</v>
+        <v>6.18</v>
       </c>
       <c r="V2" t="n">
-        <v>7.38</v>
+        <v>6.06</v>
       </c>
       <c r="W2" t="n">
-        <v>6.44</v>
+        <v>5.91</v>
       </c>
       <c r="X2" t="n">
-        <v>6.76</v>
+        <v>6.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.73</v>
+        <v>6.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.38</v>
+        <v>6.06</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.44</v>
+        <v>5.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.76</v>
+        <v>6.14</v>
       </c>
       <c r="AC2" t="n">
         <v>0.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1752019200</v>
@@ -4379,407 +4384,410 @@
         <v>0.71</v>
       </c>
       <c r="AH2" t="n">
-        <v>129</v>
+        <v>0.435</v>
       </c>
       <c r="AI2" t="n">
-        <v>21.499998</v>
+        <v>120.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>31201400</v>
+        <v>20.066666</v>
       </c>
       <c r="AK2" t="n">
-        <v>31201400</v>
+        <v>23735636</v>
       </c>
       <c r="AL2" t="n">
-        <v>32348776</v>
+        <v>23735636</v>
       </c>
       <c r="AM2" t="n">
-        <v>44574797</v>
+        <v>28692207</v>
       </c>
       <c r="AN2" t="n">
-        <v>44574797</v>
+        <v>29819552</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.45</v>
+        <v>29819552</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.46</v>
+        <v>6.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>6547644416</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>6547644666</v>
+        <v>6111134720</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>6273557215</v>
       </c>
       <c r="AV2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AW2" t="n">
         <v>9.09</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>12.245</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>1.975</v>
       </c>
-      <c r="AY2" t="n">
-        <v>2.7092998</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>6.9588</v>
+        <v>2.5286798</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.208</v>
+        <v>6.7904</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>7.1682</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="BE2" t="b">
+      <c r="BF2" t="b">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
-        <v>7050158080</v>
-      </c>
       <c r="BG2" t="n">
+        <v>6628164096</v>
+      </c>
+      <c r="BH2" t="n">
         <v>0.02476</v>
       </c>
-      <c r="BH2" t="n">
-        <v>750307067</v>
-      </c>
       <c r="BI2" t="n">
+        <v>751974149</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1015138708</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>0.22922</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>0.00068999996</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1015138708</v>
       </c>
-      <c r="BM2" t="n">
-        <v>2.503</v>
-      </c>
       <c r="BN2" t="n">
-        <v>2.5769076</v>
+        <v>2.497</v>
       </c>
       <c r="BO2" t="n">
+        <v>2.4108932</v>
+      </c>
+      <c r="BP2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BS2" t="n">
         <v>-0.291</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BT2" t="n">
         <v>59832432</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
         <v>0.05</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="BV2" t="n">
         <v>0.3</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>20:10</t>
         </is>
       </c>
-      <c r="BW2" t="n">
+      <c r="BX2" t="n">
         <v>1461888000</v>
       </c>
-      <c r="BX2" t="n">
-        <v>2.917</v>
-      </c>
       <c r="BY2" t="n">
-        <v>58.497</v>
+        <v>2.743</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.05286342</v>
+        <v>55.526</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27697718</v>
+        <v>-0.03888023</v>
       </c>
       <c r="CB2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CC2" t="n">
         <v>0.03</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CD2" t="n">
         <v>1752019200</v>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CE2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CF2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>815112576</v>
       </c>
-      <c r="CH2" t="n">
-        <v>0.805</v>
-      </c>
       <c r="CI2" t="n">
-        <v>120521600</v>
+        <v>0.803</v>
       </c>
       <c r="CJ2" t="n">
+        <v>119370632</v>
+      </c>
+      <c r="CK2" t="n">
         <v>1343206016</v>
       </c>
-      <c r="CK2" t="n">
-        <v>0.619</v>
-      </c>
       <c r="CL2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="CM2" t="n">
         <v>1.241</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>2416729344</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>53.215</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>2.203</v>
       </c>
-      <c r="CP2" t="n">
-        <v>-0.00059</v>
-      </c>
       <c r="CQ2" t="n">
+        <v>-0.00071000005</v>
+      </c>
+      <c r="CR2" t="n">
         <v>0.02183</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>277897888</v>
       </c>
-      <c r="CS2" t="n">
-        <v>49947636</v>
-      </c>
       <c r="CT2" t="n">
+        <v>50759544</v>
+      </c>
+      <c r="CU2" t="n">
         <v>166570720</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>-0.289</v>
       </c>
-      <c r="CV2" t="n">
+      <c r="CW2" t="n">
         <v>0.076</v>
       </c>
-      <c r="CW2" t="n">
+      <c r="CX2" t="n">
         <v>0.114989996</v>
       </c>
-      <c r="CX2" t="n">
-        <v>0.04987</v>
-      </c>
       <c r="CY2" t="n">
-        <v>0.0018099999</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+        <v>0.049390003</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.02098</v>
+      </c>
+      <c r="DA2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>002510.SZ</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="DG2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>-0.15999985</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>5.91 - 6.14</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>28692207</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.11000013</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.018612545</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>5.91 - 9.09</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>-3.0700002</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.33773378</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-3.888023</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1619607540</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1619607540</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1290648600000</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-2.5889945</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.77040005</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.1134543</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-1.1482</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.16017969</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>Tianjin Motor Dies Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>1780038267</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EK2" t="n">
+        <v>1782111885</v>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EM2" t="inlineStr">
         <is>
           <t>finmb_47065418</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DN2" t="n">
+      <c r="EP2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DP2" t="b">
+      <c r="ER2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
-        <v>-0.5088</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.07311606399999999</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.7580004</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Tianjin Motor Dies Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>TIANJIN MOTOR DIES CO LTD</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>Tianjin Motor Dies Co.,Ltd.</t>
         </is>
       </c>
-      <c r="EB2" t="n">
-        <v>-4.1604786</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1290648600000</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.2800002</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>6.44 - 6.76</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>32348776</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.040322583</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>6.2 - 9.09</t>
-        </is>
-      </c>
-      <c r="EM2" t="n">
-        <v>-2.6400003</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.2904291</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>-5.2863417</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1619607540</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1619607540</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.10516098</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
